--- a/data/trans_bre/P45C_R1-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R1-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,92</t>
+          <t>-3,37; 0,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,63</t>
+          <t>-1,02; 2,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,02</t>
+          <t>-0,72; 3,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 2,43</t>
+          <t>-3,07; 2,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-76,98; 63,32</t>
+          <t>-80,13; 64,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,93; 420,14</t>
+          <t>-62,75; 364,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 673,12</t>
+          <t>-37,78; 547,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 818,7</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,37</t>
+          <t>-1,52; 1,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,36</t>
+          <t>-3,01; 0,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,13</t>
+          <t>-1,29; 1,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,23</t>
+          <t>-3,18; 2,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,15; 112,03</t>
+          <t>-61,44; 123,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,61; 26,16</t>
+          <t>-79,36; 21,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,9; 198,14</t>
+          <t>-72,22; 216,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,12; 224,0</t>
+          <t>-76,06; 310,16</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,21</t>
+          <t>0,41; 3,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,18</t>
+          <t>0,43; 3,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,27</t>
+          <t>-1,44; 0,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,59</t>
+          <t>-1,8; 1,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,6; 742,48</t>
+          <t>3,66; 681,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,34; 1331,14</t>
+          <t>14,1; 1758,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 92,79</t>
+          <t>-92,78; 133,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-60,32; 150,75</t>
+          <t>-58,66; 146,62</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,15</t>
+          <t>-2,68; 1,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,35</t>
+          <t>-0,81; 2,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,65</t>
+          <t>0,32; 2,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,87</t>
+          <t>-1,0; 1,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,98; 86,47</t>
+          <t>-76,37; 85,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,91; 258,57</t>
+          <t>-38,54; 279,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,3; —</t>
+          <t>-23,73; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 328,22</t>
+          <t>-45,22; 266,95</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,09</t>
+          <t>-1,33; 2,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,62</t>
+          <t>-0,98; 1,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,31</t>
+          <t>-1,33; 1,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,45</t>
+          <t>-2,35; 0,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-66,3; 361,7</t>
+          <t>-73,67; 429,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-71,42; 41,27</t>
+          <t>-72,63; 53,46</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,29</t>
+          <t>-2,07; 1,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,65</t>
+          <t>-1,6; 1,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,82</t>
+          <t>-2,21; 0,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,63</t>
+          <t>-1,08; 0,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-97,27; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-91,07; 366,27</t>
+          <t>-89,92; 357,76</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,17</t>
+          <t>-3,19; 0,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,64</t>
+          <t>-1,69; 0,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,27</t>
+          <t>-1,39; 0,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,6</t>
+          <t>-0,67; 0,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,87</t>
+          <t>-0,3; 0,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,71</t>
+          <t>-0,29; 0,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,47</t>
+          <t>-0,94; 0,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 44,34</t>
+          <t>-33,1; 47,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 86,68</t>
+          <t>-21,59; 83,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 100,73</t>
+          <t>-26,87; 106,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 37,47</t>
+          <t>-44,58; 38,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P45C_R1-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R1-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-13,41%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,79</t>
+          <t>-3,03; 0,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,56</t>
+          <t>-0,86; 2,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,7</t>
+          <t>-0,79; 3,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 2,44</t>
+          <t>-2,21; 3,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-80,13; 64,72</t>
+          <t>-77,98; 58,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-62,75; 364,75</t>
+          <t>-52,74; 485,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 547,1</t>
+          <t>-43,82; 624,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 818,7</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,44</t>
+          <t>-1,69; 1,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,29</t>
+          <t>-3,16; 0,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,15</t>
+          <t>-1,29; 1,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,36</t>
+          <t>-2,45; 2,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,44; 123,7</t>
+          <t>-61,51; 130,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,36; 21,42</t>
+          <t>-78,04; 30,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,22; 216,22</t>
+          <t>-69,28; 226,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,06; 310,16</t>
+          <t>-68,61; 312,43</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,6%</t>
+          <t>-7,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,3</t>
+          <t>0,39; 3,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,18</t>
+          <t>0,52; 3,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,33</t>
+          <t>-1,5; 0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,55</t>
+          <t>-1,82; 1,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 681,3</t>
+          <t>10,33; 794,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,1; 1758,27</t>
+          <t>20,22; 1299,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-92,78; 133,75</t>
+          <t>-100,0; 121,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,66; 146,62</t>
+          <t>-60,93; 113,86</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>-13,14%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,05</t>
+          <t>-2,66; 1,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,28</t>
+          <t>-0,89; 2,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,41</t>
+          <t>0,29; 2,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,65</t>
+          <t>-2,19; 1,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,37; 85,6</t>
+          <t>-77,18; 105,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,54; 279,32</t>
+          <t>-44,85; 246,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,73; —</t>
+          <t>-20,1; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 266,95</t>
+          <t>-63,57; 77,71</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-34,63%</t>
+          <t>-30,36%</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,15</t>
+          <t>-1,12; 2,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,57</t>
+          <t>-1,02; 1,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,4</t>
+          <t>-1,34; 1,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,61</t>
+          <t>-2,1; 0,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-73,67; 429,76</t>
+          <t>-60,41; 386,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 53,46</t>
+          <t>-68,5; 72,64</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-10,77%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,06</t>
+          <t>-1,65; 1,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,61</t>
+          <t>-1,36; 1,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,8</t>
+          <t>-2,21; 0,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,71</t>
+          <t>-1,02; 0,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-89,92; 357,76</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-57,41%</t>
+          <t>-57,19%</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,18</t>
+          <t>-3,39; 0,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,64</t>
+          <t>-1,38; 0,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,22</t>
+          <t>-1,41; 0,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-11,78%</t>
+          <t>-9,87%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,65</t>
+          <t>-0,63; 0,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,88</t>
+          <t>-0,25; 0,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,72</t>
+          <t>-0,29; 0,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,44</t>
+          <t>-0,8; 0,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 47,06</t>
+          <t>-31,66; 48,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 83,81</t>
+          <t>-15,74; 84,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 106,1</t>
+          <t>-26,14; 101,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 38,0</t>
+          <t>-38,07; 35,07</t>
         </is>
       </c>
     </row>
